--- a/public/files/en/p4-p6-curriculum-gap-map.xlsx
+++ b/public/files/en/p4-p6-curriculum-gap-map.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Suggested P4-P6 goal (check against F pp.1-6 to 1-10)</t>
+          <t>Suggested P4-P6 goal (check against the learning progression in the official documents)</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>□ Each activity can be tied to the EDB framework (F pp.1-6 to 1-10 or B p.2)</t>
+          <t>□ Each activity can be tied to a planning requirement or learning progression in the official documents</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>The three schools below are fictional, shown for illustration only. The "covered / partial / empty" judgements use the suggested goal list above and are not the EDB's assessment of any school.</t>
+          <t>The three schools below are fictional, shown for illustration only. The "covered / partial / empty" judgements use the suggested goal list above and are not an assessment of any school.</t>
         </is>
       </c>
     </row>
@@ -1319,20 +1319,6 @@
       <c r="A91" t="inlineStr">
         <is>
           <t>The key judgement: a school starting from nothing runs the G2 and G3 pilots first; "discuss next term" is a legitimate next step provided the meeting actually sets a review date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>How this relates to the EDB framework</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Maps to F (the AI Literacy Learning Framework for Primary and Secondary Schools, pp.1-6 to 1-10): cross-subject implementation and progression across four learning stages, used to check a school's own activities against the stage goals; and B (the Blueprint for Digital Education Development in Primary and Secondary Schools (three-fold leaflet), p.2): digital and AI education strategies in school development plans with a clear implementation timetable.</t>
         </is>
       </c>
     </row>
